--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6797,7 +6797,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3285-265-CM26</t>
+          <t>5110-216-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1234.02</v>
+        <v>656.88</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5110-216-CM26</t>
+          <t>3285-265-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,17 +6878,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>656.88</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="107">
@@ -7285,7 +7285,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2306-531-CM26</t>
+          <t>4832-334-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14097.22</v>
+        <v>2855.75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2307-797-CM26</t>
+          <t>1057539-4447-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.547.970-k</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1273.99</v>
+        <v>5940.34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1057539-4447-CM26</t>
+          <t>2307-797-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,17 +7427,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.547.970-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5940.34</v>
+        <v>1273.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4832-334-CM26</t>
+          <t>2306-531-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2855.75</v>
+        <v>14097.22</v>
       </c>
     </row>
     <row r="117">
@@ -7834,7 +7834,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>387-416-CM26</t>
+          <t>2328-808-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2431.17</v>
+        <v>10746.24</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2328-808-CM26</t>
+          <t>387-416-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>10746.24</v>
+        <v>2431.17</v>
       </c>
     </row>
     <row r="124">
@@ -8444,7 +8444,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>582-61-CM26</t>
+          <t>3723-84-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>60.511.104-1</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>807.3</v>
+        <v>2281.23</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3723-84-CM26</t>
+          <t>582-61-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>60.511.104-1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2281.23</v>
+        <v>807.3</v>
       </c>
     </row>
     <row r="134">
@@ -8871,7 +8871,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2328-958-CM26</t>
+          <t>2328-961-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>11859.09</v>
+        <v>9592.59</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2328-961-CM26</t>
+          <t>2328-958-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,7 +8987,68 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>9592.59</v>
+        <v>11859.09</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2324-1140-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>4239.14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2328-1427-CM25</t>
+          <t>387-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23526</v>
+        <v>10103.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2328-1432-CM25</t>
+          <t>3479-91-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5937.62</v>
+        <v>2648.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1409-126-CM25</t>
+          <t>2324-145-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28688.45</v>
+        <v>9662.799999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2854-1585-CM25</t>
+          <t>387-160-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22580.25</v>
+        <v>9792.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2852-1175-CM25</t>
+          <t>2324-463-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6295.1</v>
+        <v>18596.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2852-1187-CM25</t>
+          <t>2328-288-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20824.7</v>
+        <v>10349.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3888-684-CM25</t>
+          <t>2306-200-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4584.64</v>
+        <v>10412.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>387-831-CM25</t>
+          <t>2306-343-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4781.78</v>
+        <v>42303.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2989-887-CM25</t>
+          <t>2324-655-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11539.19</v>
+        <v>6481.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3888-760-CM25</t>
+          <t>3507-452-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5051.85</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>752-507-CM25</t>
+          <t>2324-903-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,33 +1179,33 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>43590.27</v>
+        <v>10995.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2328-3593-CM25</t>
+          <t>2324-942-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>17528.7</v>
+        <v>8494.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2328-3595-CM25</t>
+          <t>1126922-1457-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35057.4</v>
+        <v>6625.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>752-522-CM25</t>
+          <t>1126922-1486-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,43 +1362,43 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5233.03</v>
+        <v>3777.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2658-1792-CM25</t>
+          <t>4939-398-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.231.100-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE CHAITEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2389.42</v>
+        <v>10338.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1126922-2961-CM25</t>
+          <t>2328-1427-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>26116.55</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1126922-2960-CM25</t>
+          <t>2328-1432-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>30054.76</v>
+        <v>5937.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3926-1061-CM25</t>
+          <t>1409-126-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1606,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1856.36</v>
+        <v>28688.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3926-1062-CM25</t>
+          <t>2854-1585-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4464.46</v>
+        <v>22580.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2324-4-CM26</t>
+          <t>2852-1175-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7176.56</v>
+        <v>6295.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2660-1-CM26</t>
+          <t>2852-1187-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,43 +1789,43 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>55641.27</v>
+        <v>20824.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2324-18-CM26</t>
+          <t>3888-684-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2628.59</v>
+        <v>4584.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3723-3-CM26</t>
+          <t>2989-887-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>791</v>
+        <v>11539.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3723-4-CM26</t>
+          <t>387-831-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1009.12</v>
+        <v>4781.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1007793-4-CM26</t>
+          <t>3888-760-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>63660.7</v>
+        <v>5051.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2307-101-CM26</t>
+          <t>752-507-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2538.94</v>
+        <v>43590.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1007793-13-CM26</t>
+          <t>752-522-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1365.07</v>
+        <v>5233.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>584146-25-CM26</t>
+          <t>2328-3595-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2435.78</v>
+        <v>35057.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2328-44-CM26</t>
+          <t>2328-3593-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>51170.12</v>
+        <v>17528.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1071775-14-CM26</t>
+          <t>2658-1792-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12852</v>
+        <v>2389.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2324-104-CM26</t>
+          <t>1126922-2960-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2260.41</v>
+        <v>30054.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2324-105-CM26</t>
+          <t>1126922-2961-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>10667.21</v>
+        <v>26116.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2306-11-CM26</t>
+          <t>3926-1061-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>31225.6</v>
+        <v>1856.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2297-81-CM26</t>
+          <t>3926-1062-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4977</v>
+        <v>4464.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3504-279-CM26</t>
+          <t>2324-4-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.230.300-8</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE DALCAHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>24453.01</v>
+        <v>7176.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1393093-107-CM26</t>
+          <t>2660-1-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>18525.02</v>
+        <v>55641.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2297-169-CM26</t>
+          <t>2324-18-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>967.47</v>
+        <v>2628.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2297-177-CM26</t>
+          <t>3723-4-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>967.47</v>
+        <v>1009.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4832-117-CM26</t>
+          <t>3723-3-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3807.99</v>
+        <v>791</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3285-73-CM26</t>
+          <t>1007793-4-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>61.999.290-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1937.08</v>
+        <v>63660.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>752-38-CM26</t>
+          <t>2307-101-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12864.5</v>
+        <v>2538.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2863-17-CM26</t>
+          <t>1007793-13-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.210.400-5</t>
+          <t>61.999.290-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3180.93</v>
+        <v>1365.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2912-107-CM26</t>
+          <t>584146-25-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1147.16</v>
+        <v>2435.78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3723-23-CM26</t>
+          <t>2324-105-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>972.23</v>
+        <v>10667.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3723-24-CM26</t>
+          <t>2328-44-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>578.34</v>
+        <v>51170.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3479-417-CM26</t>
+          <t>1071775-14-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5277.21</v>
+        <v>12852</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3723-26-CM26</t>
+          <t>2324-104-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>967.47</v>
+        <v>2260.41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>507428-280-CM26</t>
+          <t>2306-11-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8008.7</v>
+        <v>31225.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5423-63-CM26</t>
+          <t>2297-81-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4780.83</v>
+        <v>4977</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1393093-349-CM26</t>
+          <t>3504-279-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.230.300-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE DALCAHUE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1217.37</v>
+        <v>24453.01</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2297-366-CM26</t>
+          <t>1393093-107-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2148.87</v>
+        <v>18525.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5413-208-CM26</t>
+          <t>2297-169-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>23883.3</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3507-213-CM26</t>
+          <t>2297-177-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4880.19</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4042-55-CM26</t>
+          <t>4832-117-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.220.402-6</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8430.110000000001</v>
+        <v>3807.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2306-139-CM26</t>
+          <t>3285-73-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>28476.18</v>
+        <v>1937.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1126922-241-CM26</t>
+          <t>752-38-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>672.95</v>
+        <v>12864.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2324-427-CM26</t>
+          <t>2863-17-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.400-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1431.36</v>
+        <v>3180.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4939-120-CM26</t>
+          <t>2912-107-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.231.100-0</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHAITEN</t>
+          <t>Departamento Administrativo de Salud Municipal.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>21896</v>
+        <v>1147.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2912-158-CM26</t>
+          <t>3723-23-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1273.99</v>
+        <v>972.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5110-110-CM26</t>
+          <t>3723-24-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10013.28</v>
+        <v>578.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>584146-137-CM26</t>
+          <t>3479-417-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3452.04</v>
+        <v>5277.21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2852-215-CM26</t>
+          <t>3723-26-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>31706.36</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2886-35-CM26</t>
+          <t>507428-280-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1738.59</v>
+        <v>8008.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2328-316-CM26</t>
+          <t>5423-63-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>33929.92</v>
+        <v>4780.83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3723-34-CM26</t>
+          <t>1393093-349-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1009.12</v>
+        <v>1217.37</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4090-117-CM26</t>
+          <t>3507-213-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>911.3</v>
+        <v>4880.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4090-120-CM26</t>
+          <t>2297-366-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,27 +4550,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ASOPCON LIMITADA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.404.551-3</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>386.04</v>
+        <v>2148.87</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4090-121-CM26</t>
+          <t>5413-208-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13129.51</v>
+        <v>23883.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>934-42-CM26</t>
+          <t>4042-55-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.220.402-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Ilustre Municipalidad de Fresia - Salud</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1237.6</v>
+        <v>8430.110000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5423-141-CM26</t>
+          <t>2306-139-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3842.51</v>
+        <v>28476.18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2306-244-CM26</t>
+          <t>1126922-241-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>20134.8</v>
+        <v>672.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3443-328-CM26</t>
+          <t>2324-427-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>65462.66</v>
+        <v>1431.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1393093-416-CM26</t>
+          <t>4939-120-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.231.100-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE CHAITEN</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>71828.39999999999</v>
+        <v>21896</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1393093-417-CM26</t>
+          <t>584146-137-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>10788.54</v>
+        <v>3452.04</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1393093-418-CM26</t>
+          <t>2912-158-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>Departamento Administrativo de Salud Municipal.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>54806.64</v>
+        <v>1273.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1393093-420-CM26</t>
+          <t>5110-110-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>65698.71000000001</v>
+        <v>10013.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1393093-421-CM26</t>
+          <t>2852-215-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>48569.85</v>
+        <v>31706.36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2940-52-CM26</t>
+          <t>2886-35-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.210.201-0</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>11792.25</v>
+        <v>1738.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2940-53-CM26</t>
+          <t>2328-316-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.210.201-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1408.82</v>
+        <v>33929.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1037-35-CM26</t>
+          <t>3723-34-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,27 +5343,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2072.74</v>
+        <v>1009.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3507-306-CM26</t>
+          <t>4090-117-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2694.16</v>
+        <v>911.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2328-457-CM26</t>
+          <t>4090-120-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>ASOPCON LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.404.551-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8165.73</v>
+        <v>386.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2328-464-CM26</t>
+          <t>4090-121-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3659.96</v>
+        <v>13129.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3285-209-CM26</t>
+          <t>934-42-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3084.09</v>
+        <v>1237.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2328-492-CM26</t>
+          <t>2306-244-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>650.73</v>
+        <v>20134.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4939-172-CM26</t>
+          <t>5423-141-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.231.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHAITEN</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>11400.2</v>
+        <v>3842.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3443-406-CM26</t>
+          <t>3443-328-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>6802.94</v>
+        <v>65462.66</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3443-405-CM26</t>
+          <t>1393093-421-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,27 +5831,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1038.87</v>
+        <v>48569.85</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4090-182-CM26</t>
+          <t>1393093-420-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2618</v>
+        <v>65698.71000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1393093-486-CM26</t>
+          <t>1393093-416-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>39134.34</v>
+        <v>71828.39999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1393093-487-CM26</t>
+          <t>1393093-417-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>26784.52</v>
+        <v>10788.54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1126922-637-CM26</t>
+          <t>1393093-418-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1157.87</v>
+        <v>54806.64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>752-138-CM26</t>
+          <t>2940-52-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,27 +6136,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>IMunicipalidad de San Pablo - Educación</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2022.95</v>
+        <v>11792.25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1037-43-CM26</t>
+          <t>2940-53-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.210.201-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>IMunicipalidad de San Pablo - Educación</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2838.98</v>
+        <v>1408.82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2852-485-CM26</t>
+          <t>1037-35-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7790.34</v>
+        <v>2072.74</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2306-365-CM26</t>
+          <t>3507-306-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Departamento de Salud</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10257.21</v>
+        <v>2694.16</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3285-256-CM26</t>
+          <t>2328-457-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Tic Services SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3807.23</v>
+        <v>8165.73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>387-345-CM26</t>
+          <t>2328-464-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>707.34</v>
+        <v>3659.96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>387-346-CM26</t>
+          <t>3285-209-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1511.28</v>
+        <v>3084.09</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1393093-518-CM26</t>
+          <t>2328-492-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1675.52</v>
+        <v>650.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>707425-104-CM26</t>
+          <t>4939-172-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.231.100-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CHAITEN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>468.03</v>
+        <v>11400.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2289-540-CM26</t>
+          <t>3443-405-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3941.28</v>
+        <v>1038.87</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2289-541-CM26</t>
+          <t>3443-406-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>606.89</v>
+        <v>6802.94</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5110-216-CM26</t>
+          <t>4090-182-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>656.88</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3285-265-CM26</t>
+          <t>1393093-486-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1234.02</v>
+        <v>39134.34</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2854-693-CM26</t>
+          <t>1393093-487-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,27 +6929,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>27364.76</v>
+        <v>26784.52</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1126922-765-CM26</t>
+          <t>1126922-637-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,17 +6990,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>27807.44</v>
+        <v>1157.87</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2328-714-CM26</t>
+          <t>752-138-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>971.85</v>
+        <v>2022.95</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5423-280-CM26</t>
+          <t>1037-43-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2035.57</v>
+        <v>2838.98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2306-498-CM26</t>
+          <t>2852-485-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,27 +7173,27 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4244.02</v>
+        <v>7790.34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2289-582-CM26</t>
+          <t>2306-365-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3794.01</v>
+        <v>10257.21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4832-334-CM26</t>
+          <t>3285-256-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2855.75</v>
+        <v>3807.23</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1057539-4447-CM26</t>
+          <t>387-345-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.547.970-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5940.34</v>
+        <v>707.34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2307-797-CM26</t>
+          <t>387-346-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1273.99</v>
+        <v>1511.28</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2306-531-CM26</t>
+          <t>1393093-518-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>14097.22</v>
+        <v>1675.52</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2862-73-CM26</t>
+          <t>707425-104-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.210.400-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2019.43</v>
+        <v>468.03</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1007793-119-CM26</t>
+          <t>2289-541-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2862.35</v>
+        <v>606.89</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2328-784-CM26</t>
+          <t>2289-540-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7661,27 +7661,27 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7025.76</v>
+        <v>3941.28</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5413-662-CM26</t>
+          <t>5110-216-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>9889.02</v>
+        <v>656.88</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5413-663-CM26</t>
+          <t>3285-265-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,27 +7783,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7784.46</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2328-808-CM26</t>
+          <t>2854-693-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>10746.24</v>
+        <v>27364.76</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>387-416-CM26</t>
+          <t>1126922-765-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2431.17</v>
+        <v>27807.44</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5413-681-CM26</t>
+          <t>2328-714-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,27 +7966,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2688.81</v>
+        <v>971.85</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1393093-580-CM26</t>
+          <t>5423-280-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4942.77</v>
+        <v>2035.57</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1393093-581-CM26</t>
+          <t>2306-498-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,27 +8088,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8473.32</v>
+        <v>4244.02</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3507-468-CM26</t>
+          <t>2289-582-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2118.33</v>
+        <v>3794.01</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>387-435-CM26</t>
+          <t>2306-531-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1012.69</v>
+        <v>14097.22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2307-852-CM26</t>
+          <t>2307-797-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8271,17 +8271,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4065.92</v>
+        <v>1273.99</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5413-728-CM26</t>
+          <t>4832-334-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8332,27 +8332,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>999.73</v>
+        <v>2855.75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1393093-586-CM26</t>
+          <t>1057539-4447-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.547.970-k</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>25761.73</v>
+        <v>5940.34</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3723-84-CM26</t>
+          <t>2862-73-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.210.400-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2281.23</v>
+        <v>2019.43</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>582-61-CM26</t>
+          <t>1007793-119-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.511.104-1</t>
+          <t>61.999.290-3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>807.3</v>
+        <v>2862.35</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1126922-951-CM26</t>
+          <t>2328-784-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>969.84</v>
+        <v>7025.76</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1126922-959-CM26</t>
+          <t>5413-662-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>968.65</v>
+        <v>9889.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2328-906-CM26</t>
+          <t>5413-663-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>10714.57</v>
+        <v>7784.46</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1426102-130-CM26</t>
+          <t>387-416-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1334.29</v>
+        <v>2431.17</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4090-329-CM26</t>
+          <t>2328-808-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3566.91</v>
+        <v>10746.24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2328-961-CM26</t>
+          <t>5413-681-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>9592.59</v>
+        <v>2688.81</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2328-958-CM26</t>
+          <t>1393093-580-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>11859.09</v>
+        <v>4942.77</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2324-1140-CM26</t>
+          <t>1393093-581-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,6 +9048,921 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
+        <v>8473.32</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>3507-468-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>65.321.890-7</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Departamento de Salud</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>2118.33</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>387-435-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>69.220.800-5</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>IMPORTADORA HEVIA SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>76.872.717-1</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>1012.69</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2307-852-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>4065.92</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>5413-728-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AURA XD SPA </t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>76.359.312-6</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>999.73</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1393093-586-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>25761.73</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>582-61-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>60.511.104-1</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tic Services SPA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>807.3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>3723-84-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>69.230.800-k</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>2281.23</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1126922-951-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>969.84</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1126922-959-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>968.65</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2328-906-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>10714.57</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1426102-130-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>1334.29</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4090-329-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>69.220.500-6</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>3566.91</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2328-961-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>9592.59</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2328-958-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>11859.09</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2324-1140-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
         <v>4239.14</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
@@ -684,7 +684,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2801,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2866,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2931,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2996,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3183,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3309,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3435,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3500,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3565,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3630,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3695,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3760,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3886,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3951,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4077,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4203,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4268,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4230,7 +4398,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4291,7 +4463,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4352,7 +4528,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4593,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4658,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4723,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4849,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4914,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +4979,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5105,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5023,7 +5231,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5145,7 +5357,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5422,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5328,7 +5548,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5389,7 +5613,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5511,7 +5739,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5572,7 +5804,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5633,7 +5869,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +5934,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5755,7 +5999,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +6064,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5877,7 +6129,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5938,7 +6194,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5999,7 +6259,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6060,7 +6324,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6121,7 +6389,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6454,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6243,7 +6519,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6584,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6832,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6897,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7084,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7271,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7336,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7401,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7466,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7531,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7596,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7722,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7463,7 +7787,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7852,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +7917,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +7982,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +8047,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7768,7 +8112,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8177,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8242,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8307,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8372,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8437,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8502,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8567,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8632,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8697,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8762,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8827,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8892,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9018,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9083,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9148,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9213,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9278,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9343,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9408,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9049,7 +9473,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9538,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9603,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9668,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9733,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9798,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9863,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9928,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +9993,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +10119,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9720,7 +10184,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10249,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10375,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10440,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10147,7 +10627,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10692,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10757,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10822,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10887,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +10952,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +11017,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +11082,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10696,7 +11208,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11273,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11338,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11403,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11468,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11001,7 +11533,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11598,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11663,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11850,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11489,7 +12037,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +12102,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12228,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11733,7 +12293,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12358,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12423,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12549,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12614,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12740,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +12866,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +12931,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +12996,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +13061,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +13187,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +13252,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13378,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13443,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12892,7 +13508,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13573,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13075,7 +13699,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13764,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +13829,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +13894,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +13959,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13380,7 +14024,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13441,7 +14089,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +14215,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13624,7 +14280,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14406,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14471,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14536,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14601,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13990,7 +14666,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14731,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14796,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14173,7 +14861,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14234,7 +14926,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14356,7 +15052,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +15117,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14478,7 +15182,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15308,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15373,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15438,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15503,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15568,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14905,7 +15633,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14966,7 +15698,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15027,7 +15763,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15088,7 +15828,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15893,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +16019,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15332,7 +16084,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +16271,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16336,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16401,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16527,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15820,7 +16592,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15881,7 +16657,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +16783,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +16848,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +16913,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16186,7 +16978,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16247,7 +17043,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17108,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17173,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16430,7 +17238,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17303,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17368,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17494,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17559,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17624,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17750,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17815,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +17880,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17945,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +18010,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +18136,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18201,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18266,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +18331,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18396,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18461,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18587,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18713,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +18778,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18843,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M287"/>
+  <dimension ref="A1:M292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2436,7 +2436,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2306-343-CM25</t>
+          <t>2306-337-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2476,28 +2476,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>42303.43</v>
+        <v>7703.11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2306-337-CM25</t>
+          <t>2306-343-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2537,26 +2541,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7703.11</v>
+        <v>42303.43</v>
       </c>
     </row>
     <row r="34">
@@ -3968,7 +3968,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5413-703-CM25</t>
+          <t>507428-3195-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4008,28 +4008,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2416.68</v>
+        <v>16802.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>507428-3195-CM25</t>
+          <t>5413-703-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4054,12 +4058,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4069,26 +4073,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>16802.8</v>
+        <v>2416.68</v>
       </c>
     </row>
     <row r="58">
@@ -4155,7 +4155,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2863-46-CM25</t>
+          <t>507428-3224-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.210.400-5</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4557.64</v>
+        <v>401388.19</v>
       </c>
     </row>
     <row r="60">
@@ -4285,7 +4285,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>507428-3224-CM25</t>
+          <t>2863-46-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.210.400-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD PUERTO OCTAY</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>401388.19</v>
+        <v>4557.64</v>
       </c>
     </row>
     <row r="62">
@@ -4675,7 +4675,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1126922-1457-CM25</t>
+          <t>1126922-1406-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4715,12 +4715,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>6625.78</v>
+        <v>4101.79</v>
       </c>
     </row>
     <row r="68">
@@ -4801,7 +4801,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1126922-1406-CM25</t>
+          <t>1126922-1457-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4101.79</v>
+        <v>6625.78</v>
       </c>
     </row>
     <row r="70">
@@ -4996,7 +4996,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1126922-1501-CM25</t>
+          <t>1126922-1485-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5036,28 +5036,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8043.21</v>
+        <v>6264.16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1126922-1498-CM25</t>
+          <t>1126922-1500-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5097,32 +5101,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5137.23</v>
+        <v>7134.17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1126922-1500-CM25</t>
+          <t>1126922-1501-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7134.17</v>
+        <v>8043.21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1126922-1485-CM25</t>
+          <t>1126922-1498-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6264.16</v>
+        <v>5137.23</v>
       </c>
     </row>
     <row r="76">
@@ -5374,7 +5374,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1071775-89-CM25</t>
+          <t>2306-937-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5414,32 +5414,28 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3968.48</v>
+        <v>10834.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2306-937-CM25</t>
+          <t>1071775-89-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5464,12 +5460,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5479,22 +5475,26 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10834.95</v>
+        <v>3968.48</v>
       </c>
     </row>
     <row r="80">
@@ -5951,7 +5951,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1126922-1766-CM25</t>
+          <t>2854-1115-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3153.05</v>
+        <v>21919.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2854-1115-CM25</t>
+          <t>1126922-1766-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>21919.8</v>
+        <v>3153.05</v>
       </c>
     </row>
     <row r="89">
@@ -6146,7 +6146,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1393093-1123-CM25</t>
+          <t>1393093-1126-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6205,13 +6205,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>50527.1</v>
+        <v>48332.67</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1393093-1126-CM25</t>
+          <t>1393093-1124-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6270,13 +6270,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>48332.67</v>
+        <v>53444.84</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1393093-1124-CM25</t>
+          <t>1393093-1123-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>53444.84</v>
+        <v>50527.1</v>
       </c>
     </row>
     <row r="93">
@@ -6662,7 +6662,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2328-1183-CM25</t>
+          <t>2328-1185-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6702,22 +6702,26 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7996.68</v>
+        <v>18285.54</v>
       </c>
     </row>
     <row r="99">
@@ -6784,7 +6788,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2328-1185-CM25</t>
+          <t>2328-1183-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6824,26 +6828,22 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>18285.54</v>
+        <v>7996.68</v>
       </c>
     </row>
     <row r="101">
@@ -6914,7 +6914,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>584146-514-CM25</t>
+          <t>752-410-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3648.37</v>
+        <v>4248.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>752-410-CM25</t>
+          <t>584146-514-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4248.3</v>
+        <v>3648.37</v>
       </c>
     </row>
     <row r="104">
@@ -7739,7 +7739,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2989-887-CM25</t>
+          <t>387-831-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7798,13 +7798,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>11539.19</v>
+        <v>4781.78</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>387-831-CM25</t>
+          <t>2989-887-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4781.78</v>
+        <v>11539.19</v>
       </c>
     </row>
     <row r="117">
@@ -8129,7 +8129,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2328-3593-CM25</t>
+          <t>608897-11419-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8149,17 +8149,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8169,17 +8169,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8188,13 +8188,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>17528.7</v>
+        <v>3398.76</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>608897-11419-CM25</t>
+          <t>752-522-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8234,17 +8234,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8253,13 +8253,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3398.76</v>
+        <v>5233.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>752-522-CM25</t>
+          <t>2328-3593-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8279,17 +8279,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5233.03</v>
+        <v>17528.7</v>
       </c>
     </row>
     <row r="124">
@@ -9100,7 +9100,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1007793-13-CM26</t>
+          <t>584146-25-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9140,17 +9140,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9159,13 +9159,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1365.07</v>
+        <v>2435.78</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>584146-25-CM26</t>
+          <t>1007793-13-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.999.290-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9224,13 +9224,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2435.78</v>
+        <v>1365.07</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2328-44-CM26</t>
+          <t>2324-105-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9270,12 +9270,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>51170.12</v>
+        <v>10667.21</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1071775-14-CM26</t>
+          <t>2324-104-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9354,13 +9354,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>12852</v>
+        <v>2260.41</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2324-104-CM26</t>
+          <t>2328-44-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2260.41</v>
+        <v>51170.12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2324-105-CM26</t>
+          <t>1071775-14-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>10667.21</v>
+        <v>12852</v>
       </c>
     </row>
     <row r="142">
@@ -9880,7 +9880,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2297-177-CM26</t>
+          <t>4832-117-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9900,17 +9900,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9920,17 +9920,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9939,13 +9939,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>967.47</v>
+        <v>3807.99</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4832-117-CM26</t>
+          <t>2297-177-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9965,17 +9965,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9985,17 +9985,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3807.99</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="150">
@@ -10392,7 +10392,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3479-417-CM26</t>
+          <t>3723-26-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10412,17 +10412,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10432,32 +10432,28 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5277.21</v>
+        <v>967.47</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3723-26-CM26</t>
+          <t>507428-280-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10477,17 +10473,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10497,12 +10493,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10512,13 +10508,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>967.47</v>
+        <v>8008.7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>507428-280-CM26</t>
+          <t>3479-417-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10543,12 +10539,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10558,22 +10554,26 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>8008.7</v>
+        <v>5277.21</v>
       </c>
     </row>
     <row r="159">
@@ -11034,7 +11034,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1126922-241-CM26</t>
+          <t>2324-427-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11074,32 +11074,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>672.95</v>
+        <v>1431.36</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2324-427-CM26</t>
+          <t>1126922-241-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11124,12 +11120,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11139,22 +11135,26 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1431.36</v>
+        <v>672.95</v>
       </c>
     </row>
     <row r="168">
@@ -11225,7 +11225,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2852-215-CM26</t>
+          <t>5110-110-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11245,17 +11245,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11284,13 +11284,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>31706.36</v>
+        <v>10013.28</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2912-158-CM26</t>
+          <t>584146-137-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11315,12 +11315,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.220.702-5</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11330,12 +11330,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11349,13 +11349,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1273.99</v>
+        <v>3452.04</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5110-110-CM26</t>
+          <t>2912-158-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.702-5</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -11414,13 +11414,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>10013.28</v>
+        <v>1273.99</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>584146-137-CM26</t>
+          <t>2852-215-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11440,17 +11440,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3452.04</v>
+        <v>31706.36</v>
       </c>
     </row>
     <row r="173">
@@ -11680,7 +11680,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4090-120-CM26</t>
+          <t>4090-121-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>ASOPCON LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.404.551-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11735,13 +11735,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>386.04</v>
+        <v>13129.51</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3723-34-CM26</t>
+          <t>4090-120-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11761,17 +11761,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ASOPCON LIMITADA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.404.551-3</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11796,13 +11796,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1009.12</v>
+        <v>386.04</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4090-117-CM26</t>
+          <t>3723-34-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11842,32 +11842,28 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>911.3</v>
+        <v>1009.12</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4090-121-CM26</t>
+          <t>4090-117-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11907,22 +11903,26 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>13129.51</v>
+        <v>911.3</v>
       </c>
     </row>
     <row r="180">
@@ -12180,7 +12180,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1393093-420-CM26</t>
+          <t>1393093-418-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12239,13 +12239,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>65698.71000000001</v>
+        <v>54806.64</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1393093-418-CM26</t>
+          <t>1393093-420-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12304,13 +12304,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>54806.64</v>
+        <v>65698.71000000001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1393093-421-CM26</t>
+          <t>1393093-417-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12369,13 +12369,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>48569.85</v>
+        <v>10788.54</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1393093-416-CM26</t>
+          <t>1393093-421-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>71828.39999999999</v>
+        <v>48569.85</v>
       </c>
     </row>
     <row r="188">
@@ -12501,7 +12501,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1393093-417-CM26</t>
+          <t>1393093-416-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>10788.54</v>
+        <v>71828.39999999999</v>
       </c>
     </row>
     <row r="190">
@@ -13139,7 +13139,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3443-405-CM26</t>
+          <t>3443-406-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13179,17 +13179,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13198,13 +13198,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1038.87</v>
+        <v>6802.94</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3443-406-CM26</t>
+          <t>3443-405-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13244,17 +13244,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13263,13 +13263,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>6802.94</v>
+        <v>1038.87</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4090-182-CM26</t>
+          <t>1393093-486-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13289,17 +13289,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13309,28 +13309,32 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2618</v>
+        <v>39134.34</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1393093-486-CM26</t>
+          <t>1393093-487-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13370,12 +13374,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -13389,13 +13393,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>39134.34</v>
+        <v>26784.52</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1393093-487-CM26</t>
+          <t>1126922-637-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13420,12 +13424,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13435,12 +13439,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13454,13 +13458,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>26784.52</v>
+        <v>1157.87</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1126922-637-CM26</t>
+          <t>4090-182-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13480,17 +13484,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13500,26 +13504,22 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1157.87</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="205">
@@ -13781,7 +13781,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3285-256-CM26</t>
+          <t>387-345-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13840,13 +13840,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3807.23</v>
+        <v>707.34</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>387-345-CM26</t>
+          <t>1393093-518-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>707.34</v>
+        <v>1675.52</v>
       </c>
     </row>
     <row r="211">
@@ -13976,7 +13976,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1393093-518-CM26</t>
+          <t>3285-256-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1675.52</v>
+        <v>3807.23</v>
       </c>
     </row>
     <row r="213">
@@ -14232,7 +14232,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3285-265-CM26</t>
+          <t>5110-216-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14252,17 +14252,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.231.000-4</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14272,32 +14272,28 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1234.02</v>
+        <v>656.88</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5110-216-CM26</t>
+          <t>3285-265-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14317,17 +14313,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.231.000-4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE CURACO DE VELEZ</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14337,22 +14333,26 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>656.88</v>
+        <v>1234.02</v>
       </c>
     </row>
     <row r="218">
@@ -14813,7 +14813,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2306-531-CM26</t>
+          <t>4832-334-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14833,17 +14833,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14853,17 +14853,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>14097.22</v>
+        <v>2855.75</v>
       </c>
     </row>
     <row r="226">
@@ -14943,7 +14943,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1057539-4447-CM26</t>
+          <t>2306-531-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14983,28 +14983,32 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.547.970-k</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>5940.34</v>
+        <v>14097.22</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4832-334-CM26</t>
+          <t>1057539-4447-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15024,17 +15028,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15044,26 +15048,22 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>SERVICIOS Y SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>78.547.970-k</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2855.75</v>
+        <v>5940.34</v>
       </c>
     </row>
     <row r="229">
@@ -15390,7 +15390,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>387-416-CM26</t>
+          <t>2328-808-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15415,12 +15415,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15430,17 +15430,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15449,13 +15449,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2431.17</v>
+        <v>10746.24</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2328-808-CM26</t>
+          <t>387-416-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15495,17 +15495,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>10746.24</v>
+        <v>2431.17</v>
       </c>
     </row>
     <row r="236">
@@ -16036,7 +16036,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>582-61-CM26</t>
+          <t>3723-84-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16061,12 +16061,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>60.511.104-1</t>
+          <t>69.230.800-k</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16076,32 +16076,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>807.3</v>
+        <v>2281.23</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3723-84-CM26</t>
+          <t>582-61-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16126,12 +16122,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.230.800-k</t>
+          <t>60.511.104-1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16141,22 +16137,26 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2281.23</v>
+        <v>807.3</v>
       </c>
     </row>
     <row r="246">
@@ -16479,7 +16479,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2328-961-CM26</t>
+          <t>2328-958-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -16538,13 +16538,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9592.59</v>
+        <v>11859.09</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2328-958-CM26</t>
+          <t>2328-961-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>11859.09</v>
+        <v>9592.59</v>
       </c>
     </row>
     <row r="253">
@@ -16674,7 +16674,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4180-130-CM26</t>
+          <t>2324-1069-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16714,28 +16714,32 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
+          <t>77.508.642-4</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>6477.17</v>
+        <v>3179.07</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2324-1069-CM26</t>
+          <t>4180-130-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16760,12 +16764,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16775,26 +16779,22 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3179.07</v>
+        <v>6477.17</v>
       </c>
     </row>
     <row r="256">
@@ -17320,7 +17320,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2307-1068-CM26</t>
+          <t>387-547-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17345,12 +17345,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17360,32 +17360,28 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5090.68</v>
+        <v>847.8200000000001</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>387-547-CM26</t>
+          <t>2307-1068-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17410,12 +17406,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17425,28 +17421,32 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>847.8200000000001</v>
+        <v>5090.68</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2660-65-CM26</t>
+          <t>4091-345-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.230.100-5</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANCUD</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17486,17 +17486,17 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17505,13 +17505,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>9821.209999999999</v>
+        <v>7386.13</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4091-345-CM26</t>
+          <t>2660-65-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17536,12 +17536,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.230.100-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17551,17 +17551,17 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -17570,7 +17570,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>7386.13</v>
+        <v>9821.209999999999</v>
       </c>
     </row>
     <row r="268">
@@ -17702,7 +17702,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1393093-751-CM26</t>
+          <t>1126922-1305-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17727,12 +17727,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17761,13 +17761,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>5796.49</v>
+        <v>1012.69</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1126922-1305-CM26</t>
+          <t>1393093-751-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17787,17 +17787,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1012.69</v>
+        <v>5796.49</v>
       </c>
     </row>
     <row r="272">
@@ -18027,7 +18027,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>582-71-CM26</t>
+          <t>5413-986-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>60.511.104-1</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18067,28 +18067,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3148.74</v>
+        <v>18940.81</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5413-986-CM26</t>
+          <t>5413-988-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18128,12 +18132,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -18147,13 +18151,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>18940.81</v>
+        <v>4740.41</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5413-988-CM26</t>
+          <t>582-71-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18173,17 +18177,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>60.511.104-1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHILOÉ</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18193,26 +18197,22 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>4740.41</v>
+        <v>3148.74</v>
       </c>
     </row>
     <row r="278">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -18348,7 +18348,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1577-185-CM26</t>
+          <t>752-267-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18368,17 +18368,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.511.100-9</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS LAGOS</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18388,12 +18388,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -18407,13 +18407,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3152.31</v>
+        <v>9979.26</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>752-267-CM26</t>
+          <t>752-268-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18453,32 +18453,28 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>9979.26</v>
+        <v>2391.77</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>752-268-CM26</t>
+          <t>2328-1311-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18503,12 +18499,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18518,28 +18514,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2391.77</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2328-1311-CM26</t>
+          <t>1577-185-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18564,12 +18564,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.511.100-9</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18665,7 +18665,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2852-1027-CM26</t>
+          <t>1393093-793-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18685,17 +18685,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18705,12 +18705,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18724,13 +18724,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>8975.99</v>
+        <v>30392.01</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1393093-793-CM26</t>
+          <t>2852-1027-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18755,12 +18755,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18770,12 +18770,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18789,7 +18789,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>30392.01</v>
+        <v>8975.99</v>
       </c>
     </row>
     <row r="287">
@@ -18855,6 +18855,315 @@
       </c>
       <c r="M287" s="2" t="n">
         <v>3213</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2852-1059-CM26</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="n">
+        <v>34955.73</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>752-291-CM26</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>72.221.800-0</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="n">
+        <v>42869.45</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>5413-1112-CM26</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>982.7</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>752-299-CM26</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>72.221.800-0</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="n">
+        <v>27119.33</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2852-1118-CM26</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="n">
+        <v>4175.19</v>
       </c>
     </row>
   </sheetData>
